--- a/Exc2/Проверочный лист для аудита ИБ.xlsx
+++ b/Exc2/Проверочный лист для аудита ИБ.xlsx
@@ -30,7 +30,6 @@
   <si>
     <t>Используется ли многофакторная аутентификация (MFA) для доступа к критическим системам и сервисам?</t>
   </si>
-  <si/>
   <si>
     <t>Недостаточно данных</t>
   </si>
@@ -379,11 +378,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
   <numFmts>
-    <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1001"/>
-    <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1003"/>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1002"/>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1000"/>
-    <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1004"/>
+    <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1001"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -681,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="1" fillId="2" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
@@ -705,7 +702,6 @@
       <alignment horizontal="left" indent="1" vertical="center" wrapText="true"/>
     </xf>
     <xf applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="1" numFmtId="1001" quotePrefix="false"/>
-    <xf applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="5" fillId="3" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -715,9 +711,6 @@
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="7" fillId="3" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="1" numFmtId="1002" quotePrefix="false">
-      <alignment horizontal="left" indent="1" vertical="center" wrapText="true"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="8" fillId="3" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -727,7 +720,7 @@
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="10" fillId="3" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="2" numFmtId="1003" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="2" numFmtId="1002" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="11" fillId="3" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,16 +760,13 @@
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="23" fillId="4" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="17" fillId="4" fontId="2" numFmtId="1004" quotePrefix="false">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="24" fillId="4" fontId="2" numFmtId="1004" quotePrefix="false">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="25" fillId="4" fontId="2" numFmtId="1004" quotePrefix="false">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="26" fillId="4" fontId="2" numFmtId="1004" quotePrefix="false">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="24" fillId="4" fontId="2" numFmtId="1000" quotePrefix="false">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="25" fillId="4" fontId="2" numFmtId="1000" quotePrefix="false">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="26" fillId="4" fontId="2" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,7 +990,7 @@
     <col customWidth="true" max="3" min="3" outlineLevel="0" width="7.74574728906965"/>
     <col customWidth="true" max="4" min="4" outlineLevel="0" width="29.734420936548"/>
     <col customWidth="true" max="5" min="5" outlineLevel="0" width="10.5665866003129"/>
-    <col customWidth="true" max="6" min="6" outlineLevel="0" width="35.2296611922799"/>
+    <col customWidth="true" max="6" min="6" outlineLevel="0" width="70.7973461886098"/>
   </cols>
   <sheetData>
     <row customHeight="true" ht="27" outlineLevel="0" r="3">
@@ -1032,11 +1022,9 @@
       <c r="D5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>7</v>
       </c>
     </row>
     <row customHeight="true" ht="61.5" outlineLevel="0" r="6">
@@ -1044,11 +1032,11 @@
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="9" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="80.25" outlineLevel="0" r="7">
@@ -1056,11 +1044,11 @@
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="9" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="77.25" outlineLevel="0" r="8">
@@ -1068,13 +1056,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row customHeight="true" ht="87.75" outlineLevel="0" r="9">
@@ -1082,11 +1070,11 @@
         <v>5</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="9" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="69" outlineLevel="0" r="10">
@@ -1094,11 +1082,11 @@
         <v>6</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="9" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="82.5" outlineLevel="0" r="11">
@@ -1106,13 +1094,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row customHeight="true" ht="62.25" outlineLevel="0" r="12">
@@ -1120,13 +1108,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row customHeight="true" ht="55.5" outlineLevel="0" r="13">
@@ -1134,13 +1122,13 @@
         <v>9</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row customHeight="true" ht="62.4000015258789" outlineLevel="0" r="14">
@@ -1148,13 +1136,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row customHeight="true" ht="62.4000015258789" outlineLevel="0" r="15">
@@ -1162,13 +1150,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row customHeight="true" ht="68.25" outlineLevel="0" r="16">
@@ -1176,13 +1164,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row customHeight="true" ht="52.7999992370605" outlineLevel="0" r="17">
@@ -1190,13 +1178,11 @@
         <v>13</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>6</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="60.75" outlineLevel="0" r="18">
@@ -1204,33 +1190,33 @@
         <v>14</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row customHeight="true" ht="36.75" outlineLevel="0" r="19">
       <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="10" t="s"/>
-      <c r="E19" s="11" t="s"/>
-      <c r="F19" s="12" t="s"/>
+        <v>32</v>
+      </c>
+      <c r="D19" s="9" t="s"/>
+      <c r="E19" s="10" t="s"/>
+      <c r="F19" s="11" t="s"/>
     </row>
     <row customHeight="true" ht="75.75" outlineLevel="0" r="20">
       <c r="C20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="63.75" outlineLevel="0" r="21">
@@ -1238,11 +1224,11 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="54" outlineLevel="0" r="22">
@@ -1250,11 +1236,11 @@
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="s">
-        <v>9</v>
+        <v>35</v>
+      </c>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="82.5" outlineLevel="0" r="23">
@@ -1262,13 +1248,13 @@
         <v>4</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row customHeight="true" ht="64.5" outlineLevel="0" r="24">
@@ -1276,11 +1262,11 @@
         <v>5</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="9" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="56.25" outlineLevel="0" r="25">
@@ -1288,11 +1274,11 @@
         <v>6</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="9" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="125.25" outlineLevel="0" r="26">
@@ -1300,13 +1286,13 @@
         <v>7</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row customHeight="true" ht="90" outlineLevel="0" r="27">
@@ -1314,41 +1300,37 @@
         <v>8</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row customHeight="true" ht="55.5" outlineLevel="0" r="28">
       <c r="C28" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>46</v>
+      <c r="D28" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>6</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row customHeight="true" ht="51.75" outlineLevel="0" r="29">
       <c r="C29" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>6</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="53.25" outlineLevel="0" r="30">
@@ -1356,73 +1338,69 @@
         <v>11</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>6</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row customHeight="true" ht="52.5" outlineLevel="0" r="31">
       <c r="C31" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="9" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row customHeight="true" ht="51" outlineLevel="0" r="32">
       <c r="C32" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="9" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row customHeight="true" ht="48.75" outlineLevel="0" r="33">
       <c r="C33" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="29.25" outlineLevel="0" r="34">
       <c r="C34" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="14" t="s"/>
-      <c r="E34" s="15" t="s"/>
-      <c r="F34" s="16" t="s"/>
+        <v>51</v>
+      </c>
+      <c r="D34" s="12" t="s"/>
+      <c r="E34" s="13" t="s"/>
+      <c r="F34" s="14" t="s"/>
     </row>
     <row customHeight="true" ht="69" outlineLevel="0" r="35">
       <c r="C35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row customHeight="true" ht="90.75" outlineLevel="0" r="36">
@@ -1430,13 +1408,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row customHeight="true" ht="80.25" outlineLevel="0" r="37">
@@ -1444,13 +1422,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row customHeight="true" ht="70.5" outlineLevel="0" r="38">
@@ -1458,13 +1436,11 @@
         <v>4</v>
       </c>
       <c r="D38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="15" t="s">
         <v>59</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row customHeight="true" ht="80.25" outlineLevel="0" r="39">
@@ -1472,11 +1448,11 @@
         <v>5</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="9" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="82.5" outlineLevel="0" r="40">
@@ -1484,11 +1460,11 @@
         <v>6</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="9" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="81" outlineLevel="0" r="41">
@@ -1496,11 +1472,11 @@
         <v>7</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="9" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="78.75" outlineLevel="0" r="42">
@@ -1508,11 +1484,11 @@
         <v>8</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="9" t="n"/>
+        <v>63</v>
+      </c>
+      <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="93.75" outlineLevel="0" r="43">
@@ -1520,11 +1496,11 @@
         <v>9</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="9" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="63.75" outlineLevel="0" r="44">
@@ -1532,11 +1508,11 @@
         <v>10</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="9" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="53.25" outlineLevel="0" r="45">
@@ -1544,13 +1520,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row customHeight="true" ht="54.75" outlineLevel="0" r="46">
@@ -1558,33 +1534,33 @@
         <v>12</v>
       </c>
       <c r="D46" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row customHeight="true" ht="24.75" outlineLevel="0" r="47">
       <c r="C47" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="18" t="s"/>
-      <c r="E47" s="19" t="s"/>
-      <c r="F47" s="20" t="s"/>
+        <v>70</v>
+      </c>
+      <c r="D47" s="16" t="s"/>
+      <c r="E47" s="17" t="s"/>
+      <c r="F47" s="18" t="s"/>
     </row>
     <row customHeight="true" ht="82.5" outlineLevel="0" r="48">
       <c r="C48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="9" t="n"/>
+        <v>71</v>
+      </c>
+      <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="101.25" outlineLevel="0" r="49">
@@ -1592,11 +1568,11 @@
         <v>2</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="9" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="105.75" outlineLevel="0" r="50">
@@ -1604,11 +1580,11 @@
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="9" t="n"/>
+        <v>73</v>
+      </c>
+      <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="80.25" outlineLevel="0" r="51">
@@ -1616,11 +1592,11 @@
         <v>4</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="9" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="88.5" outlineLevel="0" r="52">
@@ -1628,11 +1604,11 @@
         <v>5</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="9" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="90.75" outlineLevel="0" r="53">
@@ -1640,42 +1616,42 @@
         <v>6</v>
       </c>
       <c r="D53" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row customHeight="true" ht="24" outlineLevel="0" r="54">
       <c r="C54" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" s="21" t="s"/>
-      <c r="E54" s="22" t="s"/>
-      <c r="F54" s="23" t="s"/>
+        <v>78</v>
+      </c>
+      <c r="D54" s="19" t="s"/>
+      <c r="E54" s="20" t="s"/>
+      <c r="F54" s="21" t="s"/>
     </row>
     <row customHeight="true" ht="24" outlineLevel="0" r="55">
       <c r="B55" s="0" t="n"/>
-      <c r="C55" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D55" s="25" t="s"/>
-      <c r="E55" s="26" t="s"/>
-      <c r="F55" s="27" t="s"/>
+      <c r="C55" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="23" t="s"/>
+      <c r="E55" s="24" t="s"/>
+      <c r="F55" s="25" t="s"/>
     </row>
     <row customHeight="true" ht="102.75" outlineLevel="0" r="56">
       <c r="C56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" s="9" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="69" outlineLevel="0" r="57">
@@ -1683,11 +1659,11 @@
         <v>2</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" s="9" t="n"/>
+        <v>81</v>
+      </c>
+      <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="93.75" outlineLevel="0" r="58">
@@ -1695,11 +1671,11 @@
         <v>3</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="9" t="n"/>
+        <v>82</v>
+      </c>
+      <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="78.75" outlineLevel="0" r="59">
@@ -1707,31 +1683,31 @@
         <v>4</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customHeight="true" ht="25.5" outlineLevel="0" r="60">
+      <c r="C60" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row customHeight="true" ht="25.5" outlineLevel="0" r="60">
-      <c r="C60" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="28" t="s"/>
-      <c r="E60" s="29" t="s"/>
-      <c r="F60" s="30" t="s"/>
+      <c r="D60" s="26" t="s"/>
+      <c r="E60" s="27" t="s"/>
+      <c r="F60" s="28" t="s"/>
     </row>
     <row customHeight="true" ht="67.5" outlineLevel="0" r="61">
       <c r="C61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="9" t="n"/>
+        <v>85</v>
+      </c>
+      <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84" outlineLevel="0" r="62">
@@ -1739,11 +1715,11 @@
         <v>2</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" s="9" t="n"/>
+        <v>86</v>
+      </c>
+      <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="63">
@@ -1751,33 +1727,33 @@
         <v>3</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E63" s="9" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="32.25" outlineLevel="0" r="64">
       <c r="A64" s="0" t="n"/>
       <c r="B64" s="0" t="n"/>
-      <c r="C64" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" s="32" t="s"/>
-      <c r="E64" s="33" t="s"/>
-      <c r="F64" s="34" t="s"/>
+      <c r="C64" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="29" t="s"/>
+      <c r="E64" s="30" t="s"/>
+      <c r="F64" s="31" t="s"/>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="65">
       <c r="C65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E65" s="9" t="n"/>
+        <v>89</v>
+      </c>
+      <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="66">
@@ -1785,11 +1761,11 @@
         <v>2</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E66" s="9" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="67">
@@ -1797,13 +1773,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="68">
@@ -1811,11 +1787,11 @@
         <v>4</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E68" s="9" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="69">
@@ -1823,11 +1799,11 @@
         <v>5</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E69" s="9" t="n"/>
+        <v>94</v>
+      </c>
+      <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="70">
@@ -1835,25 +1811,23 @@
         <v>6</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>6</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row customHeight="true" ht="84.75" outlineLevel="0" r="71">
       <c r="C71" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="9" t="n"/>
+        <v>96</v>
+      </c>
+      <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
